--- a/nostroy-leadgen/nostroy.xlsx
+++ b/nostroy-leadgen/nostroy.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НОСТРОЙ (реестр СРО)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'НОСТРОЙ (реестр СРО)'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'НОСТРОЙ (реестр СРО)'!$A$1:$N$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,10 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -518,8 +521,3548 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Cтроительная компания «ДомСтрой»</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>7705552444</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1147746116033</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация по содействию строительным организациям в осуществлении ими профессиональной деятельности «Альянс Строителей Столицы»</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-19T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Генеральный директор Егоркин Евгений Николаевич</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OOO "Сахалин Газ Сервис"</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ООО "СГС"</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>6501272528</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1156501002283</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Региональное отраслевое объединение работодателей - Саморегулируемая организация в области строительства «СпецСтройРеконструкция»</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Сахалинская обл</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2017-03-06T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Табакова Елена Юрьевна</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>41.20</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>693017, САХАЛИНСКАЯ ОБЛАСТЬ, Г. ЮЖНО-САХАЛИНСК, ПРОМЫШЛЕННЫЙ РАЙОН ЛИСТВЕННИЧНОЕ, УЛ. 4-Я ЗАРЕЧНАЯ, Д. 28 "Б"</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>OOO "Строительная коммерческая  компания "АВИТА"</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ООО СКК "АВИТА"</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6500000899</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1026500540846</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Региональное отраслевое объединение работодателей - Саморегулируемая организация в области строительства «СпецСтройРеконструкция»</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Сахалинская обл</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2017-03-02T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Ким Вадим Ченманович</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41.20.9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>г Южно-Сахалинск, ул Пуркаева М.А., д 33/1, помещ 5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>OOO Строительно-монтажная компания "СахСтройСервис"</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ООО "СМК САХСТРОЙСЕРВИС"</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6501266500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1146501005793</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Региональное отраслевое объединение работодателей - Саморегулируемая организация в области строительства «СпецСтройРеконструкция»</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Сахалинская обл</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2017-05-04T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Тихонов Сергей Иванович</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43.22</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>г Южно-Сахалинск, Энергетиков пер, д 1Д/2, офис 5</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>OOO "СтройБат"</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ООО "СТРОЙБАТ"</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6501178211</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1076501001037</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Региональное отраслевое объединение работодателей - Саморегулируемая организация в области строительства «СпецСтройРеконструкция»</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Сахалинская обл</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2017-03-15T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Тиунцев Никита Михайлович</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>г Южно-Сахалинск, пр-кт Мира, д 2Б/8</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>OOO "Стройстандарт"</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ООО "СТРОЙСТАНДАРТ"</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5263106285</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1146507000364</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Региональное отраслевое объединение работодателей - Саморегулируемая организация в области строительства «СпецСтройРеконструкция»</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Нижегородская обл</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2017-03-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Соколова Надежда Семеновна</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>41.20</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>г Нижний Новгород, ул Энгельса, д 28, офис 9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>OOO "СЭМ"</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ООО "СЭМ"</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5610092058</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1096501004247</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Региональное отраслевое объединение работодателей - Саморегулируемая организация в области строительства «СпецСтройРеконструкция»</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Оренбургская обл</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2017-04-19T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Каширин Андрей Геннадьевич</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68.32.2</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>г Оренбург, ул Донгузская, д 8</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Oбщество с ограниченной ответственностью "СТРОЙАГРО"</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ООО "СТРОЙ АГРО"</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5257213962</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1161326058190</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация «Ассоциация строителей Мордовии»</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Нижегородская обл</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-03T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Паушкин Николай Александрович</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>41.20</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>г Нижний Новгород, ул Электровозная, д 7Б к 7, помещ 10</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая образовательная организация высшего образования "Сколковский институт науки и технологий"</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>СКОЛКОВСКИЙ ИНСТИТУТ НАУКИ И ТЕХНОЛОГИЙ, СКОЛТЕХ</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5032998454</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1115000005922</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Саморегулируемая организация «Строительные организации Москвы»</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2020-03-02T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Горбунова Юлия Германовна</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>85.22.3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, тер инновационного центра Сколково, Большой б-р, д 30 стр 1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «АВТОДОРСТРОЙТРЕСТ»</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>АНО "АДСТ"</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9709115791</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1247700612367</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строителей «Альянс Развитие»</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-21T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Дзюба Александр Александрович</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63.99.11</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Тетеринский пер, д 12 стр 2, помещ II, ком 11</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Аналитики и Высокие Технологии"</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7714524323</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1037739986030</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация строителей саморегулируемая организация "РегионСтройОбъединение"</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2015-05-28T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Генеральный директор Абрамова Екатерина Евгеньевна</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация АНО "ЦЕНТР ТВОРЧЕСКИХ И СОЦИАЛЬНЫХ ПРОГРАММ "МОЗАИКА"</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦТСП "МОЗАИКА"</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7730252243</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1197700010738</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация «Объединение строителей «ЭНЕРГОТЕХМОНТАЖ-СТРОЙ»</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Добриян Сергей Михайлович</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>90.04.2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>117149, Г.МОСКВА, ВН.ТЕР.Г. МУНИЦИПАЛЬНЫЙ ОКРУГ ЗЮЗИНО, УЛ АЗОВСКАЯ, Д. 6, К. 3, ЭТ./ПОМЕЩ. 3/№303</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Арена-2018»</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>АНО "АРЕНА-2018"</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7704279496</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1127799009095</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Некоммерческое партнёрство "Добровольное строительное товарищество "Центр специального строительства и ремонта"</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2013-02-19T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Сидоров Марат Александрович</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDATED</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>93.1</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, ул Земляной Вал, д 4 стр 1, помещ I, ком 3/4</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация в области технического регулирования и подтверждения соответствия в строительстве "ИССЛЕДОВАТЕЛЬ"</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ИССЛЕДОВАТЕЛЬ"</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2309086166</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1032304948180</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Союз «Саморегулируемая организация «Краснодарские строители»</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Краснодарский край</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2012-09-03T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Галаган Константин Викторович</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>71.20.8</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>г Краснодар, Воронежский проезд, д 5, офис 38</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>АВТОНОМНАЯ НЕКОММЕРЧЕСКАЯ ОРГАНИЗАЦИЯ ВЫСШЕГО ОБРАЗОВАНИЯ МОСКОВСКИЙ ГУМАНИТАРНО-ЭКОНОМИЧЕСКИЙ УНИВЕРСИТЕТ</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>АНО ВО МГЭУ</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7737040022</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1027700557500</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация содействия реставрации и возрождению национального архитектурного наследия «Архитектурное наследие»</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-31T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Демидова Любовь Анисимовна</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>85.22.1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Ленинский пр-кт, д 8 стр 16</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Дирекция комплексного развития территорий Ленинградской области"</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ДИРЕКЦИЯ КРТ ЛЕНИНГРАДСКОЙ ОБЛАСТИ"</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4705074009</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1174700000640</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Строительный комплекс Ленинградской области»</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Ленинградская обл</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2017-08-31T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Моргун Александр Николаевич</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>70.22</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>188641, ЛЕНИНГРАДСКАЯ ОБЛАСТЬ, М.Р-Н ВСЕВОЛОЖСКИЙ, Г.П. ВСЕВОЛОЖСКОЕ, Г. ВСЕВОЛОЖСК, УЛ. ПРИЮТИНСКАЯ, Д. 13, ПОМЕЩ. 79</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Дирекция по развитию социально значимых объектов Магаданской области»</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ДРСЗО МАГАДАНСКОЙ ОБЛАСТИ"</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4909132570</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1204900001998</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строительных организаций Восточной Сибири»</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Магаданская обл</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2021-04-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Галышин Владимир Евстахиевич</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>70.22</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>г Магадан, ул Набережная реки Магаданки, д 15, помещ 514</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Добровольная пожарная команда Ростовской области"</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ДПК РОСТОВСКОЙ ОБЛАСТИ</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6164146578</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1256100006140</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Союз «Строители Ростовской области»</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Ростовская обл</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-15T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Пилипец Василий Васильевич</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>94.99</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>г Ростов-на-Дону, ул Красноармейская, д 136</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>АВТОНОМНАЯ НЕКОММЕРЧЕСКАЯ ОРГАНИЗАЦИЯ "ИНСТИТУТ ГЕОТЕХНИКИ И ИНЖЕНЕРНОЙ ЗАЩИТЫ"</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ИГИЗ"</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7743462294</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1247700804251</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация строительных организаций «Монтаж Строительство Контроль»</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-25T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Самусевич Никита Альбертович</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>85.30</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Ленинградское шоссе, д 297</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Институт разработки и проектирования промышоенного оборудования"</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7726536764</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1067746351738</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация «Межрегиональная организация Содружество профессиональных строителей»</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2016-12-20T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Директор Давыдов Вкиторв Ханиилович</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Комплекс инжиниринговых технологий Курчатовского института"</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7734266656</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1067799026195</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация в области строительства "Межрегиональная гильдия строителей"</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2010-02-19T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Генеральный директор Стародубцев Дмитрий Геннадьевич</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Московская областная строительная центральная научно-исследовательская лаборатория"</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>АНО "МОСОБЛСТРОЙЦНИЛ"</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5024203633</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1205000024272</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Союз «Строители Московской области «Мособлстройкомплекс»</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Московская обл</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2020-04-23T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Носков Виктор Сергеевич</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>71.12.15</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Московская обл, г Красногорск, ул Ленина, д 4, ком 403</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация научно-технологический парк Оренбургского государственного университета «Технопарк ОГУ»</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ТЕХНОПАРК ОГУ"</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5612025057</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1025601806262</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Ассоциация «Альянс строителей Оренбуржья»</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Оренбургская обл</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2011-05-31T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Чирков Юрий Александрович</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>71.20.61</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>г Оренбург, пр-кт Победы, д 13, офис 1407</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Национальное экспертное объединение "СРОСЭКСПЕРТИЗА»</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>АНО "СРОСЭКСПЕРТИЗА"</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7722425213</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1177700021960</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Союз «Межрегиональное объединение инженерно-строительных предприятий»</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-13T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Шолленберг Фёдор Федорович</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>71.12.45</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>119331, Г.МОСКВА, ПР-КТ ВЕРНАДСКОГО, Д. 29, ЭТ/ПОМ/КОМ 19/1/24,25</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Операционные системные возможности"</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ОСВ"</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9703159062</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1237700721411</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация по содействию в строительстве «ПРОФЕССИОНАЛЫ СТРОИТЕЛЬНОГО КОМПЛЕКСА»</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-05T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Белоконев Александр Владимирович</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>71.12.15</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, ул Пресненский Вал, д 36 стр 2</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>АВТОНОМНАЯ НЕКОММЕРЧЕСКАЯ ОРГАНИЗАЦИЯ "ПОДДЕРЖКА СТРОИТЕЛЬСТВА СОЦИАЛЬНЫХ И ИНФРАСТРУКТУРНЫХ ОБЪЕКТОВ"</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ПССИО"</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>7720933405</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1247700497967</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация содействия реставрации и возрождению национального архитектурного наследия «Архитектурное наследие»</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-26T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Трофимова Мария Сергеевна</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>71.12.15</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Федеративный пр-кт, д 48 к 1, помещ 1/1</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по оказанию услуг в сфере жилищно- коммунального сервиса "ОМЕГА"</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3662989790</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1133600000192</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация  «Региональное объединение строителей «Развитие»</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-03T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Директор Старов Денис Витальевич</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по развитию городской среды «ГормостСтройТрест»</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ГОРМОСТСТРОЙТРЕСТ"</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9722084951</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1247700652462</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация дорожно-строительных компаний Саморегулируемая организация «Капитальный ремонт и благоустройство»</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-17T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Поляков Иван Евгеньевич</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>42.11</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Верхний Золоторожский пер, д 5 стр 3</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация ПО РАЗВИТИЮ ГОРОДСКОЙ СРЕДЫ «МОСВОДОСТОКСТРОЙТРЕСТ»</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>АНО ПО РАЗВИТИЮ ГОРОДСКОЙ СРЕДЫ "МВС СТ"</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7730328485</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1247700649570</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строителей «Альянс Развитие»</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-22T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Карапетян Георгий Грачевич</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>71.12.2</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, наб Тараса Шевченко, д 31, помещ 10</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по развитию городской среды «МОСКОЛЛЕКТОРСТРОЙТРЕСТ»</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>АНО "МКСТ"</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>9715494731</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1247700650075</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Ассоциация строительных компаний «Межрегиональный строительный комплекс»</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-27T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Андрейченко Константин Александрович</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>43.29</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, ул Поморская, д 17 стр 1</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по развитию городской среды «МосЛифтСтройТрест»</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>АНО "МЛСТ"</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>9705232014</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1247700644476</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Союз «Межрегиональное объединение организаций специального строительства»</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-22T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Трепалин Александр Евгеньевич</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>43.29</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>125040, Г.МОСКВА, ВН.ТЕР.Г. МУНИЦИПАЛЬНЫЙ ОКРУГ БЕГОВОЙ, ПР-КТ ЛЕНИНГРАДСКИЙ, Д. 26, К. 1, ЭТАЖ 2, ПОМЕЩ. I, КОМНАТЫ 51, 51Г, 51Д</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по развитию городской среды «ОЭК СТРОЙТРЕСТ»</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ОЭК СТРОЙТРЕСТ"</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>7708442087</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1247700649591</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Ассоциация строительных компаний «Межрегиональный строительный комплекс»</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-24T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Кохнович Олег Владиславович</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>43.29</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Славянская пл, д 2/5 стр 2, помещ 1</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по развитию городской среды "Строительный трест Мосгаз"</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>АНО "МОСГАЗСТРОЙТРЕСТ"</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>9709116562</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1247700649580</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация содействия развитию строительного комплекса и свободного предпринимательства в сфере строительства «Столица», саморегулируемая организация строителей</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-09T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Авраменко Артем Андреевич</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>42.21</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Мрузовский пер, д 11 стр 1, помещ 1/5, ком 8</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по реставрации и строительству православных храмов «Суморин»</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>АНО "СУМОРИН"</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3500000043</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1233500009357</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Саморегулируемая организация «Добровольное Объединение Строителей»</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Вологодская обл</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-17T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Никитин Олег Игоревич</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>41.20</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>161300, ВОЛОГОДСКАЯ ОБЛАСТЬ, М.О. ТОТЕМСКИЙ, Г. ТОТЬМА, УЛ. ЛЕСОТЕХНИКУМ, Д. 3</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация по созданию, восстановлению и организации деятельности духовно-просветительских центров «ВАЛААМ»</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ВАЛААМ"</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>7839024647</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1157800000544</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Петровское объединение строителей»</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>г Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2021-07-16T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Щеколдин Виталий Александрович</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>68.32.2</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>г Санкт-Петербург, Нарвский пр-кт, д 1/29</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>АВТОНОМНАЯ НЕКОММЕРЧЕСКАЯ ОРГАНИЗАЦИЯ "РАЗВИТИЕ ГОРОДСКИХ ТЕХНОЛОГИЙ"</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>АНО "РГТ"</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>9701170871</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1217700058146</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация содействия реставрации и возрождению национального архитектурного наследия «Архитектурное наследие»</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-27T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Бабаков Сергей Александрович</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>41.10</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, Переведеновский пер, д 13 стр 16, помещ 76/5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Региональный центр научно-технического обеспечения промышленной безопасности Северо-Западного административного округа»</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ПРОМБЕЗОПАСНОСТЬ-СЕВЕРО-ЗАПАД"</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>7825489730</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1027809215477</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Петровское объединение строителей»</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>г Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2021-07-01T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Екимов Владимир Геннадьевич</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>71.20.9</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>г Санкт-Петербург, наб Обводного канала, д 211-213 литера а, помещ 1Н</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация СОДЕЙСТВИЯ СОХРАНЕНИЮ, ВОССТАНОВЛЕНИЮ И РАЗВИТИЮ ОБЪЕКТОВ РЕЛИГИОЗНОГО, КУЛЬТУРНОГО И СОЦИАЛЬНОГО НАЗНАЧЕНИЯ «ВОЗРОЖДЕНИЕ»</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ВОЗРОЖДЕНИЕ"</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>9703188480</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1247700568620</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строителей «Альянс Развитие»</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-20T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Клюкин Михаил Васильевич</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>88.99</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>123610, Г.МОСКВА, ВН.ТЕР.Г. МУНИЦИПАЛЬНЫЙ ОКРУГ ПРЕСНЕНСКИЙ, НАБ КРАСНОПРЕСНЕНСКАЯ, Д. 12, ПОМЕЩ. 1/П</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация СОДЕЙСТВИЯ СОХРАНЕНИЮ, ВОССТАНОВЛЕНИЮ И РАЗВИТИЮ ОБЪЕКТОВ РЕЛИГИОЗНОГО, КУЛЬТУРНОГО И СОЦИАЛЬНОГО НАЗНАЧЕНИЯ «ПРЕОБРАЖЕНИЕ»</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ПРЕОБРАЖЕНИЕ"</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>9703190231</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1247700613313</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строителей «Альянс Развитие»</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-20T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Клюкин Михаил Васильевич</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>88.99</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>123610, Г.МОСКВА, ВН.ТЕР.Г. МУНИЦИПАЛЬНЫЙ ОКРУГ ПРЕСНЕНСКИЙ, НАБ КРАСНОПРЕСНЕНСКАЯ, Д. 12, ПОМЕЩ. 1/П</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация ""СОЮЗЭКСПЕРТИЗА" Торгово-промышленной палаты Российской Федерации"</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>АНО "СОЮЗЭКСПЕРТИЗА" ТПП РФ</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>7710310183</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1027739381548</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация «Московское объединение строительных предприятий малого и среднего предпринимательства – ОПОРА»</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2019-04-02T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Биматов Марат Рамилевич</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>71.20.2</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, ул Малая Дмитровка, д 13/17 стр 1</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «СТОЛИЧНЫЙ ЦЕНТР КАЧЕСТВА СТРОИТЕЛЬСТВА»</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>АНО "СЦКС"</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>7743549361</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1057746100983</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строительных организаций среднего и малого бизнеса»</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Московская обл</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-14T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Светлов Алексей Алексеевич</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>71.11.1</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Московская обл, г Видное, ул Ольховая, д 9, помещ 11</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Физкультурно-спортивный клуб Труд"</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ФСК ТРУД"</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>7717107455</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1027739830766</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Ассоциация строителей «Стройконсолидация»</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2017-06-29T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Петров Андрей Августович</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>93.11</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, проезд Ольминского, д 3А к 3</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Центр Cодействия Cтроительству Белгородской области"</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3123455934</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1193100000499</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Саморегулируемая организация «Строители Белгородской области»</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Белгородская область</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Исполнительный директор Селезнева Юлия Геннадьевна</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>АВТОНОМНАЯ НЕКОММЕРЧЕСКАЯОРГАНИЗАЦИЯ "ЦЕНТРНЕЗАВИСИМЫХ СТРОИТЕЛЬНЫХЭКСПЕРТИЗ"</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>7725352475</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1147799000194</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «СтройИндустрия»</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2014-10-15T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>ГЕНЕРАЛЬНЫЙ ДИРЕКТОР ОРЛОВ  ИВАН  АЛЕКСАНДРОВИЧ</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «ЦЕНТР ПРОГРЕССА БОКСА»</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦЕНТР ПРОГРЕССА БОКСА"</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>7704445376</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1177700017692</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Объединение строителей «Альянс Развитие»</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>г Москва</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-18T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Беспутин Александр Александрович</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>93.19</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>г Москва, ул Краснопролетарская, д 16 стр 1</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Центр развития территорий Ардатовского муниципального района Республики Мордовия»</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦЕНТР РАЗВИТИЯ ТЕРРИТОРИЙ АРДАТОВСКОГО МУНИЦИПАЛЬНОГО РАЙОНА РМ"</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>1300012513</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1241300003230</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация «Ассоциация строителей Мордовии»</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Респ Мордовия</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-13T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>94.99</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Респ Мордовия, г Ардатов, ул К.Маркса, д 160</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Центр судебных строительно-технических экспертиз и оценки зданий и сооружений»</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦССТЭО"</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2364014437</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1162300052650</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Союз «Саморегулируемая организация «Межрегиональный альянс строителей»</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Краснодарский край</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-27T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Бурцев Андрей Александрович</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>72.19.9</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>г Краснодар, ул Казбекская, д 5, офис 87-94</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Центр технических экспертиз"</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦССТЭО"</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2364014437</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1127799025012</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация «Национальное сообщество строителей»</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Краснодарский край</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2013-02-13T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Бурцев Андрей Александрович</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>72.19.9</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>г Краснодар, ул Казбекская, д 5, офис 87-94</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Центр экспертиз Торгово-промышленной палаты Нижегородской области"</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦЕНТР ЭКСПЕРТИЗ ТПП НО", АНО "ЦЭ ТПП НО"</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>5260987229</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1145200001980</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация  «Приволжская гильдия строителей»</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Нижегородская обл</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-13T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Акимова Ольга Васильевна</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>68.31.52</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>г Нижний Новгород, ул Нестерова, д 31</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Центр энергосбережения Республики Башкортостан»</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦЭРБ"</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>0277058184</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1030204445457</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация «Региональный строительный союз Республики Башкортостан»</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Респ Башкортостан</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2009-12-30T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Байков Игорь Равильевич</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>94.99</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>г Уфа, ул Северодвинская, д 12</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация «Центр энергосбережения Удмуртской Республики»</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЦЕНТР ЭНЕРГОСБЕРЕЖЕНИЯ УР"</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>1834032837</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1041803721740</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация саморегулируемая организация «Строитель»</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Удмуртская Респ</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2010-04-15T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Пьянков Алексей Сергеевич</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>70.22</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>г Ижевск, ул Карла Маркса, д 246</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая организация "Экспертно-Консультационное бюро"</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>АНО "ЭКБ"</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2634815889</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1142651030422</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация «Саморегулируемая региональная организация строителей Северного Кавказа»</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Ставропольский край</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-15T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Иванов Иван Владимирович</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>69.10</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>г Ставрополь, ул Доваторцев, д 52В</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Автономная некоммерческая профессиональная образовательная организация «Уральский политехнический колледж»</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>АНПОО УРПК</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>0273041750</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1020202386533</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Ассоциация Саморегулируемая организация «Региональный строительный союз Республики Башкортостан»</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Респ Башкортостан</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2011-06-15T00:00:00+04:00</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Минниахметов Радмир Римович</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>85.21</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>г Уфа, ул Орджоникидзе, д 20</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 13:11</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Автономное некоммерческое общество "Региональное агентство экспертизы, сертификации и аудита"</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>5036082126</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1075000003506</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Саморегулируемая организация Союз «Межрегиональное объединение инженерно-строительных предприятий»</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-11T00:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>генеральный директор Брыксин Роман Викторович</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>